--- a/Yield_Health_Tech_Startup_Costs.xlsx
+++ b/Yield_Health_Tech_Startup_Costs.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="72">
   <si>
     <t xml:space="preserve">YIELD HEALTH — TECHNOLOGY START-UP COSTS</t>
   </si>
@@ -233,6 +233,12 @@
   </si>
   <si>
     <t xml:space="preserve">Cost Mix by Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost Mix</t>
   </si>
 </sst>
 </file>
@@ -246,7 +252,7 @@
     <numFmt numFmtId="167" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -329,17 +335,11 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <color rgb="FF1E4B3A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -358,7 +358,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF8FA687"/>
-        <bgColor rgb="FF9BBB59"/>
+        <bgColor rgb="FF808080"/>
       </patternFill>
     </fill>
     <fill>
@@ -423,7 +423,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -501,6 +501,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -532,7 +540,7 @@
       <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FFC0504D"/>
+      <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFF2F2F2"/>
       <rgbColor rgb="FFE3EEE9"/>
       <rgbColor rgb="FF660066"/>
@@ -555,13 +563,13 @@
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF4F81BD"/>
+      <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF9BBB59"/>
+      <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF8064A2"/>
+      <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF8FA687"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
@@ -574,575 +582,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" u="none" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Year 1 Technology Cost by Category</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:pieChart>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Summary!B3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Year 1 Cost</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln w="12600">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:explosion val="0"/>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="4F81BD"/>
-              </a:solidFill>
-              <a:ln w="12600">
-                <a:noFill/>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="C0504D"/>
-              </a:solidFill>
-              <a:ln w="12600">
-                <a:noFill/>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="9BBB59"/>
-              </a:solidFill>
-              <a:ln w="12600">
-                <a:noFill/>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="3"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="8064A2"/>
-              </a:solidFill>
-              <a:ln w="12600">
-                <a:noFill/>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dLbls>
-            <c:dLbl>
-              <c:idx val="0"/>
-              <c:txPr>
-                <a:bodyPr wrap="none"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:separator> </c:separator>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="1"/>
-              <c:txPr>
-                <a:bodyPr wrap="none"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:separator> </c:separator>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="2"/>
-              <c:txPr>
-                <a:bodyPr wrap="none"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:separator> </c:separator>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="3"/>
-              <c:txPr>
-                <a:bodyPr wrap="none"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:separator> </c:separator>
-            </c:dLbl>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Summary!$A$4:$A$7</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Domain</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Email / Microsoft 365</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Phone System</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Platform Infrastructure</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Summary!$B$4:$B$7</c:f>
-              <c:numCache>
-                <c:formatCode>\$#,##0.00;"($"#,##0.00\);\-</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>6139.99</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>767.04</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1723.2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>17100</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:firstSliceAng val="0"/>
-      </c:pieChart>
-      <c:spPr>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-  </c:spPr>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataLabel>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <cs:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointMarkerLayout>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>151560</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>21960</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 1"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="2873880"/>
-        <a:ext cx="5039640" cy="2879640"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2048,12 +1487,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2124,6 +1564,88 @@
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="18" t="n">
+        <f aca="false">B4</f>
+        <v>6139.99</v>
+      </c>
+      <c r="C15" s="20" t="n">
+        <f aca="false">B4/$B$8</f>
+        <v>0.238629425387958</v>
+      </c>
+      <c r="D15" s="21" t="str">
+        <f aca="false">REPT("█",ROUND(C15*40,0))</f>
+        <v>██████████</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="18" t="n">
+        <f aca="false">B5</f>
+        <v>767.04</v>
+      </c>
+      <c r="C16" s="20" t="n">
+        <f aca="false">B5/$B$8</f>
+        <v>0.0298108489508255</v>
+      </c>
+      <c r="D16" s="21" t="str">
+        <f aca="false">REPT("█",ROUND(C16*40,0))</f>
+        <v>█</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="18" t="n">
+        <f aca="false">B6</f>
+        <v>1723.2</v>
+      </c>
+      <c r="C17" s="20" t="n">
+        <f aca="false">B6/$B$8</f>
+        <v>0.0669718070922802</v>
+      </c>
+      <c r="D17" s="21" t="str">
+        <f aca="false">REPT("█",ROUND(C17*40,0))</f>
+        <v>███</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="18" t="n">
+        <f aca="false">B7</f>
+        <v>17100</v>
+      </c>
+      <c r="C18" s="20" t="n">
+        <f aca="false">B7/$B$8</f>
+        <v>0.664587918568936</v>
+      </c>
+      <c r="D18" s="21" t="str">
+        <f aca="false">REPT("█",ROUND(C18*40,0))</f>
+        <v>███████████████████████████</v>
       </c>
     </row>
   </sheetData>
@@ -2138,6 +1660,5 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>